--- a/tests/fixtures/banks/ibk_sample.xlsx
+++ b/tests/fixtures/banks/ibk_sample.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>네이버파이낸셜</t>
+          <t>광고비지급</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>광고주</t>
+          <t>네이버파이낸셜</t>
         </is>
       </c>
     </row>
@@ -650,11 +650,7 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>SK에너지</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
